--- a/src/evaluation/data/processed/RES_status_quo_model_travel_time_from_sample_to_hospital.xlsx
+++ b/src/evaluation/data/processed/RES_status_quo_model_travel_time_from_sample_to_hospital.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>49.2572588</v>
+        <v>49.257259</v>
       </c>
       <c r="F2" t="n">
-        <v>6.8525412</v>
+        <v>6.852541</v>
       </c>
       <c r="G2" t="n">
         <v>15.52</v>
@@ -521,7 +521,7 @@
         <v>49.276946</v>
       </c>
       <c r="F3" t="n">
-        <v>6.8701212</v>
+        <v>6.870121</v>
       </c>
       <c r="G3" t="n">
         <v>8.92</v>
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>49.2370854</v>
+        <v>49.237085</v>
       </c>
       <c r="F4" t="n">
-        <v>6.9925905</v>
+        <v>6.99259</v>
       </c>
       <c r="G4" t="n">
         <v>8.640000000000001</v>
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49.1530091</v>
+        <v>49.153009</v>
       </c>
       <c r="F5" t="n">
-        <v>7.0483363</v>
+        <v>7.048336</v>
       </c>
       <c r="G5" t="n">
         <v>25.86</v>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.2977342</v>
+        <v>49.297734</v>
       </c>
       <c r="F6" t="n">
         <v>7.054714</v>
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.4957688</v>
+        <v>49.495769</v>
       </c>
       <c r="F7" t="n">
-        <v>6.5967711</v>
+        <v>6.596771</v>
       </c>
       <c r="G7" t="n">
         <v>30.04</v>
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>49.4957688</v>
+        <v>49.495769</v>
       </c>
       <c r="F8" t="n">
-        <v>6.5967711</v>
+        <v>6.596771</v>
       </c>
       <c r="G8" t="n">
         <v>12.08</v>
@@ -698,16 +698,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>49.4590255</v>
+        <v>49.457186</v>
       </c>
       <c r="F9" t="n">
-        <v>6.6299114</v>
+        <v>6.631578</v>
       </c>
       <c r="G9" t="n">
-        <v>12.66</v>
+        <v>11.97</v>
       </c>
       <c r="H9" t="n">
-        <v>11.26</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="10">
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>49.4590255</v>
+        <v>49.457186</v>
       </c>
       <c r="F10" t="n">
-        <v>6.6299114</v>
+        <v>6.631578</v>
       </c>
       <c r="G10" t="n">
-        <v>25.12</v>
+        <v>24.09</v>
       </c>
       <c r="H10" t="n">
-        <v>16.5</v>
+        <v>15.07</v>
       </c>
     </row>
     <row r="11">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>49.5378676</v>
+        <v>49.537868</v>
       </c>
       <c r="F11" t="n">
-        <v>6.8893404</v>
+        <v>6.88934</v>
       </c>
       <c r="G11" t="n">
         <v>9.16</v>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>49.4539793</v>
+        <v>49.453979</v>
       </c>
       <c r="F14" t="n">
-        <v>7.1784916</v>
+        <v>7.178492</v>
       </c>
       <c r="G14" t="n">
         <v>17.46</v>
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>49.3482934</v>
+        <v>49.348293</v>
       </c>
       <c r="F15" t="n">
-        <v>7.1858034</v>
+        <v>7.185803</v>
       </c>
       <c r="G15" t="n">
         <v>13.85</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>49.2661267</v>
+        <v>49.266127</v>
       </c>
       <c r="F17" t="n">
-        <v>6.6829698</v>
+        <v>6.68297</v>
       </c>
       <c r="G17" t="n">
         <v>15.68</v>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>49.3286239</v>
+        <v>49.328624</v>
       </c>
       <c r="F18" t="n">
-        <v>6.7149771</v>
+        <v>6.714977</v>
       </c>
       <c r="G18" t="n">
         <v>27.7</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>49.3152364</v>
+        <v>49.315236</v>
       </c>
       <c r="F19" t="n">
-        <v>6.7564872</v>
+        <v>6.756487</v>
       </c>
       <c r="G19" t="n">
         <v>6.64</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>49.4190916</v>
+        <v>49.419092</v>
       </c>
       <c r="F20" t="n">
         <v>6.88979</v>
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>49.4190916</v>
+        <v>49.419092</v>
       </c>
       <c r="F21" t="n">
         <v>6.88979</v>
       </c>
       <c r="G21" t="n">
-        <v>10.95</v>
+        <v>11.06</v>
       </c>
       <c r="H21" t="n">
         <v>6.04</v>
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>49.1530091</v>
+        <v>49.153009</v>
       </c>
       <c r="F22" t="n">
-        <v>7.0483363</v>
+        <v>7.048336</v>
       </c>
       <c r="G22" t="n">
         <v>19.98</v>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>49.2905518</v>
+        <v>49.290552</v>
       </c>
       <c r="F23" t="n">
-        <v>7.1131754</v>
+        <v>7.113175</v>
       </c>
       <c r="G23" t="n">
         <v>26.42</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>49.3177556</v>
+        <v>49.317756</v>
       </c>
       <c r="F24" t="n">
-        <v>7.2270153</v>
+        <v>7.227015</v>
       </c>
       <c r="G24" t="n">
         <v>20.75</v>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>49.3177556</v>
+        <v>49.317756</v>
       </c>
       <c r="F25" t="n">
-        <v>7.2270153</v>
+        <v>7.227015</v>
       </c>
       <c r="G25" t="n">
         <v>8.4</v>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>49.5378676</v>
+        <v>49.537868</v>
       </c>
       <c r="F27" t="n">
-        <v>6.8893404</v>
+        <v>6.88934</v>
       </c>
       <c r="G27" t="n">
         <v>13.41</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>49.5378676</v>
+        <v>49.537868</v>
       </c>
       <c r="F28" t="n">
-        <v>6.8893404</v>
+        <v>6.88934</v>
       </c>
       <c r="G28" t="n">
         <v>23.67</v>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>49.4539793</v>
+        <v>49.453979</v>
       </c>
       <c r="F29" t="n">
-        <v>7.1784916</v>
+        <v>7.178492</v>
       </c>
       <c r="G29" t="n">
         <v>17.76</v>
